--- a/backend/data/financials_by_company/0UNS.L.xlsx
+++ b/backend/data/financials_by_company/0UNS.L.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,55 +637,51 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="D2" t="n">
-        <v>1019381.14</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
+        <v>5558307.44</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>-5305314.7</v>
+        <v>-234631.61</v>
       </c>
       <c r="H2" t="n">
-        <v>4766000</v>
+        <v>4593000</v>
       </c>
       <c r="I2" t="n">
-        <v>27156084.36</v>
+        <v>21721546.59</v>
       </c>
       <c r="J2" t="n">
-        <v>1019381.14</v>
+        <v>5558307.44</v>
       </c>
       <c r="K2" t="n">
-        <v>-3746618.86</v>
+        <v>957604.1899999999</v>
       </c>
       <c r="L2" t="n">
-        <v>-516901.71</v>
+        <v>-449098.69</v>
       </c>
       <c r="M2" t="n">
-        <v>518206.93</v>
+        <v>475740.65</v>
       </c>
       <c r="N2" t="n">
-        <v>1305.22</v>
+        <v>26641.96</v>
       </c>
       <c r="O2" t="n">
-        <v>-5305314.7</v>
+        <v>-234631.61</v>
       </c>
       <c r="P2" t="n">
-        <v>-5305314.7</v>
+        <v>-234631.61</v>
       </c>
       <c r="Q2" t="n">
-        <v>54374604.74</v>
+        <v>43158037.77</v>
       </c>
       <c r="R2" t="n">
         <v>4750000</v>
@@ -694,129 +690,121 @@
         <v>4750000</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.116908</v>
+        <v>-0.049396</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.116908</v>
+        <v>-0.049396</v>
       </c>
       <c r="V2" t="n">
-        <v>-5305314.7</v>
+        <v>-234631.61</v>
       </c>
       <c r="W2" t="n">
-        <v>-5305314.7</v>
+        <v>-234631.61</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-5305314.7</v>
+        <v>-234631.61</v>
       </c>
       <c r="Z2" t="n">
-        <v>-5305314.7</v>
+        <v>-234610.77</v>
       </c>
       <c r="AA2" t="n">
-        <v>-5305314.7</v>
+        <v>-234610.77</v>
       </c>
       <c r="AB2" t="n">
-        <v>1040488.91</v>
+        <v>716474.3100000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>-4264825.79</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
+        <v>481863.54</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>-516901.71</v>
+        <v>-449098.69</v>
       </c>
       <c r="AG2" t="n">
-        <v>518206.93</v>
+        <v>475740.65</v>
       </c>
       <c r="AH2" t="n">
-        <v>1305.22</v>
+        <v>26641.96</v>
       </c>
       <c r="AI2" t="n">
-        <v>-3763008.04</v>
+        <v>930962.23</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27218520.38</v>
+        <v>21436491.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>9174057</v>
+        <v>7960372.56</v>
       </c>
       <c r="AL2" t="n">
-        <v>4765987.21</v>
+        <v>4600703.25</v>
       </c>
       <c r="AM2" t="n">
-        <v>4765987.21</v>
+        <v>4600703.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>23455512.34</v>
+        <v>22367453.41</v>
       </c>
       <c r="AO2" t="n">
-        <v>27156084.36</v>
+        <v>21721546.59</v>
       </c>
       <c r="AP2" t="n">
-        <v>50611596.7</v>
+        <v>44089000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>50611596.7</v>
+        <v>44089000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.15</v>
+        <v>0.224336</v>
       </c>
       <c r="D3" t="n">
-        <v>2964105.8</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
+        <v>6687649.65</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>-2486186.39</v>
+        <v>1284875.68</v>
       </c>
       <c r="H3" t="n">
-        <v>4749000</v>
+        <v>4750000</v>
       </c>
       <c r="I3" t="n">
-        <v>24463100.07</v>
+        <v>27198353.49</v>
       </c>
       <c r="J3" t="n">
-        <v>2964105.8</v>
+        <v>6687649.65</v>
       </c>
       <c r="K3" t="n">
-        <v>-1785365.69</v>
+        <v>1937618.59</v>
       </c>
       <c r="L3" t="n">
-        <v>-432318.16</v>
+        <v>-278806.78</v>
       </c>
       <c r="M3" t="n">
-        <v>440908.27</v>
+        <v>281132.83</v>
       </c>
       <c r="N3" t="n">
-        <v>8590.110000000001</v>
+        <v>2326.05</v>
       </c>
       <c r="O3" t="n">
-        <v>-2486186.39</v>
+        <v>1284875.68</v>
       </c>
       <c r="P3" t="n">
-        <v>-2486186.39</v>
+        <v>1284875.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>50013206.29</v>
+        <v>52009177.37</v>
       </c>
       <c r="R3" t="n">
         <v>4750000</v>
@@ -825,125 +813,125 @@
         <v>4750000</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.523408</v>
+        <v>0.2705</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.523408</v>
+        <v>0.2705</v>
       </c>
       <c r="V3" t="n">
-        <v>-2486186.39</v>
+        <v>1284875.68</v>
       </c>
       <c r="W3" t="n">
-        <v>-2486186.39</v>
+        <v>1284875.68</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2486186.39</v>
+        <v>1284875.68</v>
       </c>
       <c r="Z3" t="n">
-        <v>-2486186.39</v>
+        <v>1284875.68</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2486186.39</v>
+        <v>1284875.68</v>
       </c>
       <c r="AB3" t="n">
-        <v>259912.43</v>
+        <v>371610.08</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2226273.96</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
+        <v>1656485.76</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>-432318.16</v>
+        <v>-278806.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>440908.27</v>
+        <v>281132.83</v>
       </c>
       <c r="AH3" t="n">
-        <v>8590.110000000001</v>
+        <v>2326.05</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1781274.32</v>
+        <v>1935292.54</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25550106.22</v>
+        <v>24810823.88</v>
       </c>
       <c r="AK3" t="n">
-        <v>8653604.539999999</v>
+        <v>8399392.42</v>
       </c>
       <c r="AL3" t="n">
-        <v>4749471.49</v>
+        <v>4750031.06</v>
       </c>
       <c r="AM3" t="n">
-        <v>4749471.49</v>
+        <v>4750031.06</v>
       </c>
       <c r="AN3" t="n">
-        <v>23768831.9</v>
+        <v>26746116.42</v>
       </c>
       <c r="AO3" t="n">
-        <v>24463100.07</v>
+        <v>27198353.49</v>
       </c>
       <c r="AP3" t="n">
-        <v>48231931.97</v>
+        <v>53944469.91</v>
       </c>
       <c r="AQ3" t="n">
-        <v>48231931.97</v>
+        <v>53944469.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.224336</v>
+        <v>0.15</v>
       </c>
       <c r="D4" t="n">
-        <v>6687649.65</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+        <v>2964105.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
       <c r="G4" t="n">
-        <v>1284875.68</v>
+        <v>-2486186.39</v>
       </c>
       <c r="H4" t="n">
-        <v>4750000</v>
+        <v>4749000</v>
       </c>
       <c r="I4" t="n">
-        <v>27198353.49</v>
+        <v>24463100.07</v>
       </c>
       <c r="J4" t="n">
-        <v>6687649.65</v>
+        <v>2964105.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1937618.59</v>
+        <v>-1785365.69</v>
       </c>
       <c r="L4" t="n">
-        <v>-278806.78</v>
+        <v>-432318.16</v>
       </c>
       <c r="M4" t="n">
-        <v>281132.83</v>
+        <v>440908.27</v>
       </c>
       <c r="N4" t="n">
-        <v>2326.05</v>
+        <v>8590.110000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>1284875.68</v>
+        <v>-2486186.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1284875.68</v>
+        <v>-2486186.39</v>
       </c>
       <c r="Q4" t="n">
-        <v>52009177.37</v>
+        <v>50013206.29</v>
       </c>
       <c r="R4" t="n">
         <v>4750000</v>
@@ -952,121 +940,129 @@
         <v>4750000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2705</v>
+        <v>-0.523408</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2705</v>
+        <v>-0.523408</v>
       </c>
       <c r="V4" t="n">
-        <v>1284875.68</v>
+        <v>-2486186.39</v>
       </c>
       <c r="W4" t="n">
-        <v>1284875.68</v>
+        <v>-2486186.39</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1284875.68</v>
+        <v>-2486186.39</v>
       </c>
       <c r="Z4" t="n">
-        <v>1284875.68</v>
+        <v>-2486186.39</v>
       </c>
       <c r="AA4" t="n">
-        <v>1284875.68</v>
+        <v>-2486186.39</v>
       </c>
       <c r="AB4" t="n">
-        <v>371610.08</v>
+        <v>259912.43</v>
       </c>
       <c r="AC4" t="n">
-        <v>1656485.76</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+        <v>-2226273.96</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
       <c r="AF4" t="n">
-        <v>-278806.78</v>
+        <v>-432318.16</v>
       </c>
       <c r="AG4" t="n">
-        <v>281132.83</v>
+        <v>440908.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>2326.05</v>
+        <v>8590.110000000001</v>
       </c>
       <c r="AI4" t="n">
-        <v>1935292.54</v>
+        <v>-1781274.32</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24810823.88</v>
+        <v>25550106.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>8399392.42</v>
+        <v>8653604.539999999</v>
       </c>
       <c r="AL4" t="n">
-        <v>4750031.06</v>
+        <v>4749471.49</v>
       </c>
       <c r="AM4" t="n">
-        <v>4750031.06</v>
+        <v>4749471.49</v>
       </c>
       <c r="AN4" t="n">
-        <v>26746116.42</v>
+        <v>23768831.9</v>
       </c>
       <c r="AO4" t="n">
-        <v>27198353.49</v>
+        <v>24463100.07</v>
       </c>
       <c r="AP4" t="n">
-        <v>53944469.91</v>
+        <v>48231931.97</v>
       </c>
       <c r="AQ4" t="n">
-        <v>53944469.91</v>
+        <v>48231931.97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="D5" t="n">
-        <v>5558307.44</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+        <v>1019381.14</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
       <c r="G5" t="n">
-        <v>-234631.61</v>
+        <v>-5305314.7</v>
       </c>
       <c r="H5" t="n">
-        <v>4593000</v>
+        <v>4766000</v>
       </c>
       <c r="I5" t="n">
-        <v>21721546.59</v>
+        <v>27156084.36</v>
       </c>
       <c r="J5" t="n">
-        <v>5558307.44</v>
+        <v>1019381.14</v>
       </c>
       <c r="K5" t="n">
-        <v>957604.1899999999</v>
+        <v>-3746618.86</v>
       </c>
       <c r="L5" t="n">
-        <v>-449098.69</v>
+        <v>-516901.71</v>
       </c>
       <c r="M5" t="n">
-        <v>475740.65</v>
+        <v>518206.93</v>
       </c>
       <c r="N5" t="n">
-        <v>26641.96</v>
+        <v>1305.22</v>
       </c>
       <c r="O5" t="n">
-        <v>-234631.61</v>
+        <v>-5305314.7</v>
       </c>
       <c r="P5" t="n">
-        <v>-234631.61</v>
+        <v>-5305314.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>43158037.77</v>
+        <v>54355343.97</v>
       </c>
       <c r="R5" t="n">
         <v>4750000</v>
@@ -1075,72 +1071,199 @@
         <v>4750000</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.049396</v>
+        <v>-1.116908</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.049396</v>
+        <v>-1.116908</v>
       </c>
       <c r="V5" t="n">
-        <v>-234631.61</v>
+        <v>-5305314.7</v>
       </c>
       <c r="W5" t="n">
-        <v>-234631.61</v>
+        <v>-5305314.7</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-234631.61</v>
+        <v>-5305314.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>-234610.77</v>
+        <v>-5305314.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>-234610.77</v>
+        <v>-5305314.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>716474.3100000001</v>
+        <v>1040488.91</v>
       </c>
       <c r="AC5" t="n">
-        <v>481863.54</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+        <v>-4264825.79</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
       <c r="AF5" t="n">
-        <v>-449098.69</v>
+        <v>-516901.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>475740.65</v>
+        <v>518206.93</v>
       </c>
       <c r="AH5" t="n">
-        <v>26641.96</v>
+        <v>1305.22</v>
       </c>
       <c r="AI5" t="n">
-        <v>930962.23</v>
+        <v>-3743747.27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>21436491.18</v>
+        <v>27199259.61</v>
       </c>
       <c r="AK5" t="n">
-        <v>7960372.56</v>
+        <v>9441681.050000001</v>
       </c>
       <c r="AL5" t="n">
-        <v>4600703.25</v>
+        <v>4765987.21</v>
       </c>
       <c r="AM5" t="n">
-        <v>4600703.25</v>
+        <v>4765987.21</v>
       </c>
       <c r="AN5" t="n">
-        <v>22367453.41</v>
+        <v>23455512.34</v>
       </c>
       <c r="AO5" t="n">
-        <v>21721546.59</v>
+        <v>27156084.36</v>
       </c>
       <c r="AP5" t="n">
-        <v>44089000</v>
+        <v>50611596.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>44089000</v>
+        <v>50611596.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4919425.33</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>5708.23</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4608000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16776374.25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4919425.33</v>
+      </c>
+      <c r="K6" t="n">
+        <v>311302.9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-92655.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>378452.48</v>
+      </c>
+      <c r="N6" t="n">
+        <v>285797.28</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5708.23</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5708.23</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>44237601.34</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.001202</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.001202</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5708.23</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5708.23</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>5708.23</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5708.23</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5708.23</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-72857.81</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-67149.58</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>-92655.2</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>378452.48</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>285797.28</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>75654.71000000001</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>27461227.09</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>9790677.25</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4608122.43</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>4608122.43</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>27536881.8</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>16776374.25</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>44313256.05</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>44313256.05</v>
       </c>
     </row>
   </sheetData>
@@ -1154,7 +1277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1456,177 +1579,89 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>4750000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4750000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>5890164.28</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6794000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46925257.52</v>
-      </c>
-      <c r="G2" t="n">
-        <v>58199524.63</v>
-      </c>
-      <c r="H2" t="n">
-        <v>9101666.58</v>
-      </c>
-      <c r="I2" t="n">
-        <v>46925257.52</v>
-      </c>
-      <c r="J2" t="n">
-        <v>51405524.63</v>
-      </c>
-      <c r="K2" t="n">
-        <v>52504524.63</v>
-      </c>
-      <c r="L2" t="n">
-        <v>51405524.63</v>
-      </c>
-      <c r="M2" t="n">
-        <v>51405524.63</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="O2" t="n">
-        <v>6105524.64</v>
-      </c>
-      <c r="P2" t="n">
-        <v>40250000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4750000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>4750000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>17617987.32</v>
-      </c>
-      <c r="T2" t="n">
-        <v>5002486.8</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3122170.89</v>
-      </c>
-      <c r="V2" t="n">
-        <v>781315.91</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1099000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1099000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>12615500.52</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1655000</v>
-      </c>
+        <v>708085.41</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>5695000</v>
+        <v>1765000</v>
       </c>
       <c r="AB2" t="n">
-        <v>5695000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="n">
-        <v>2338157.65</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2309511.32</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>2309511.32</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>69023511.95</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>47306344.85</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="n">
-        <v>4480267.11</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2677098.88</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1803168.23</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>42826077.74</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-66840651.38</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>109666729.12</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>16312845.74</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>73516961.72</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>19836921.66</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>21717167.1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>421500.44</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>190764</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>13655602.38</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>3081698.04</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4645652.01</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5928252.33</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>6545464.56</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>903835.72</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="n">
-        <v>903835.72</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>903835.72</v>
-      </c>
+        <v>1765000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>374.88</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>129281.66</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>211242.83</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>66639754.54</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
+        <v>211242.83</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="n">
+        <v>10504957.5</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>4750000</v>
@@ -1635,38 +1670,38 @@
         <v>4750000</v>
       </c>
       <c r="D3" t="n">
-        <v>8096249.41</v>
+        <v>3241035.59</v>
       </c>
       <c r="E3" t="n">
-        <v>8476000</v>
+        <v>6367807.25</v>
       </c>
       <c r="F3" t="n">
-        <v>53061776.36</v>
+        <v>55688376.76</v>
       </c>
       <c r="G3" t="n">
-        <v>65186839.33</v>
+        <v>65754832.96</v>
       </c>
       <c r="H3" t="n">
-        <v>19242817.9</v>
+        <v>26471137.87</v>
       </c>
       <c r="I3" t="n">
-        <v>53061776.36</v>
+        <v>55688376.76</v>
       </c>
       <c r="J3" t="n">
-        <v>56710839.33</v>
+        <v>59387025.71</v>
       </c>
       <c r="K3" t="n">
-        <v>59545839.33</v>
+        <v>65754832.96</v>
       </c>
       <c r="L3" t="n">
-        <v>56710839.33</v>
+        <v>59387025.71</v>
       </c>
       <c r="M3" t="n">
-        <v>56710839.33</v>
+        <v>59387025.71</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>11410839.33</v>
+        <v>14087025.71</v>
       </c>
       <c r="P3" t="n">
         <v>40250000</v>
@@ -1678,125 +1713,121 @@
         <v>4750000</v>
       </c>
       <c r="S3" t="n">
-        <v>19143523.12</v>
+        <v>16969664.43</v>
       </c>
       <c r="T3" t="n">
-        <v>7620277.3</v>
+        <v>9860078.77</v>
       </c>
       <c r="U3" t="n">
-        <v>3584822.69</v>
+        <v>2339693.32</v>
       </c>
       <c r="V3" t="n">
-        <v>1200454.61</v>
+        <v>1152578.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2835000</v>
+        <v>6367807.25</v>
       </c>
       <c r="X3" t="n">
-        <v>2835000</v>
+        <v>6367807.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>11523245.82</v>
+        <v>7109585.66</v>
       </c>
       <c r="Z3" t="n">
-        <v>1134000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>5641000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5641000</v>
-      </c>
+        <v>1699719.69</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>2912292.75</v>
+        <v>2301395.15</v>
       </c>
       <c r="AE3" t="n">
-        <v>1759391.12</v>
+        <v>4717219.4</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>1759391.12</v>
+        <v>4717219.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>75854362.45</v>
+        <v>76356690.14</v>
       </c>
       <c r="AI3" t="n">
-        <v>45088298.73</v>
+        <v>42775966.61</v>
       </c>
       <c r="AJ3" t="n">
-        <v>176143.97</v>
+        <v>202388.61</v>
       </c>
       <c r="AK3" t="n">
-        <v>3649062.97</v>
+        <v>3698648.95</v>
       </c>
       <c r="AL3" t="n">
-        <v>1330976.38</v>
+        <v>865644</v>
       </c>
       <c r="AM3" t="n">
-        <v>2318086.59</v>
+        <v>2833004.95</v>
       </c>
       <c r="AN3" t="n">
-        <v>41439235.76</v>
+        <v>38874929.05</v>
       </c>
       <c r="AO3" t="n">
-        <v>-63148981.8</v>
+        <v>-59299962.52</v>
       </c>
       <c r="AP3" t="n">
-        <v>104588217.56</v>
+        <v>98174891.56999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13678127.26</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>9142900.9</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>69800504.95</v>
+      </c>
       <c r="AS3" t="n">
-        <v>71183766.05</v>
+        <v>69778830.28</v>
       </c>
       <c r="AT3" t="n">
-        <v>19726324.25</v>
+        <v>19253160.39</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>30766063.72</v>
+        <v>33580723.53</v>
       </c>
       <c r="AW3" t="n">
-        <v>297823.81</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>176143.97</v>
-      </c>
+        <v>1513893.53</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>21957818.77</v>
+        <v>20846649.11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3588551.11</v>
+        <v>7423565.08</v>
       </c>
       <c r="BA3" t="n">
-        <v>4855459.49</v>
+        <v>748524.73</v>
       </c>
       <c r="BB3" t="n">
-        <v>13513808.17</v>
+        <v>12674559.3</v>
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>7954526.58</v>
+        <v>8093409.23</v>
       </c>
       <c r="BE3" t="n">
-        <v>379750.59</v>
+        <v>3126771.66</v>
       </c>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
-        <v>379750.59</v>
+        <v>3126771.66</v>
       </c>
       <c r="BH3" t="n">
-        <v>379750.59</v>
+        <v>3126771.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>4750000</v>
@@ -1805,38 +1836,38 @@
         <v>4750000</v>
       </c>
       <c r="D4" t="n">
-        <v>3241035.59</v>
+        <v>8096249.41</v>
       </c>
       <c r="E4" t="n">
-        <v>6367807.25</v>
+        <v>8476000</v>
       </c>
       <c r="F4" t="n">
-        <v>55688376.76</v>
+        <v>53061776.36</v>
       </c>
       <c r="G4" t="n">
-        <v>65754832.96</v>
+        <v>65186839.33</v>
       </c>
       <c r="H4" t="n">
-        <v>26471137.87</v>
+        <v>19242817.9</v>
       </c>
       <c r="I4" t="n">
-        <v>55688376.76</v>
+        <v>53061776.36</v>
       </c>
       <c r="J4" t="n">
-        <v>59387025.71</v>
+        <v>56710839.33</v>
       </c>
       <c r="K4" t="n">
-        <v>65754832.96</v>
+        <v>59545839.33</v>
       </c>
       <c r="L4" t="n">
-        <v>59387025.71</v>
+        <v>56710839.33</v>
       </c>
       <c r="M4" t="n">
-        <v>59387025.71</v>
+        <v>56710839.33</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>14087025.71</v>
+        <v>11410839.33</v>
       </c>
       <c r="P4" t="n">
         <v>40250000</v>
@@ -1848,121 +1879,125 @@
         <v>4750000</v>
       </c>
       <c r="S4" t="n">
-        <v>16969664.43</v>
+        <v>19143523.12</v>
       </c>
       <c r="T4" t="n">
-        <v>9860078.77</v>
+        <v>7620277.3</v>
       </c>
       <c r="U4" t="n">
-        <v>2339693.32</v>
+        <v>3584822.69</v>
       </c>
       <c r="V4" t="n">
-        <v>1152578.2</v>
+        <v>1200454.61</v>
       </c>
       <c r="W4" t="n">
-        <v>6367807.25</v>
+        <v>2835000</v>
       </c>
       <c r="X4" t="n">
-        <v>6367807.25</v>
+        <v>2835000</v>
       </c>
       <c r="Y4" t="n">
-        <v>7109585.66</v>
+        <v>11523245.82</v>
       </c>
       <c r="Z4" t="n">
-        <v>1699719.69</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+        <v>1134000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5641000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>5641000</v>
+      </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>2301395.15</v>
+        <v>2912292.75</v>
       </c>
       <c r="AE4" t="n">
-        <v>4717219.4</v>
+        <v>1759391.12</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>4717219.4</v>
+        <v>1759391.12</v>
       </c>
       <c r="AH4" t="n">
-        <v>76356690.14</v>
+        <v>75854362.45</v>
       </c>
       <c r="AI4" t="n">
-        <v>42775966.61</v>
+        <v>45088298.73</v>
       </c>
       <c r="AJ4" t="n">
-        <v>202388.61</v>
+        <v>176143.97</v>
       </c>
       <c r="AK4" t="n">
-        <v>3698648.95</v>
+        <v>3649062.97</v>
       </c>
       <c r="AL4" t="n">
-        <v>865644</v>
+        <v>1330976.38</v>
       </c>
       <c r="AM4" t="n">
-        <v>2833004.95</v>
+        <v>2318086.59</v>
       </c>
       <c r="AN4" t="n">
-        <v>38874929.05</v>
+        <v>41439235.76</v>
       </c>
       <c r="AO4" t="n">
-        <v>-59299962.52</v>
+        <v>-63148981.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>98174891.56999999</v>
+        <v>104588217.56</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9142900.9</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>69800504.95</v>
-      </c>
+        <v>13678127.26</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>69778830.28</v>
+        <v>71183766.05</v>
       </c>
       <c r="AT4" t="n">
-        <v>19253160.39</v>
+        <v>19726324.25</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>33580723.53</v>
+        <v>30766063.72</v>
       </c>
       <c r="AW4" t="n">
-        <v>1513893.53</v>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+        <v>297823.81</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>176143.97</v>
+      </c>
       <c r="AY4" t="n">
-        <v>20846649.11</v>
+        <v>21957818.77</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7423565.08</v>
+        <v>3588551.11</v>
       </c>
       <c r="BA4" t="n">
-        <v>748524.73</v>
+        <v>4855459.49</v>
       </c>
       <c r="BB4" t="n">
-        <v>12674559.3</v>
+        <v>13513808.17</v>
       </c>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>8093409.23</v>
+        <v>7954526.58</v>
       </c>
       <c r="BE4" t="n">
-        <v>3126771.66</v>
+        <v>379750.59</v>
       </c>
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
-        <v>3126771.66</v>
+        <v>379750.59</v>
       </c>
       <c r="BH4" t="n">
-        <v>3126771.66</v>
+        <v>379750.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>4750000</v>
@@ -1971,38 +2006,40 @@
         <v>4750000</v>
       </c>
       <c r="D5" t="n">
-        <v>708085.41</v>
+        <v>5890236.19</v>
       </c>
       <c r="E5" t="n">
-        <v>8130426.82</v>
+        <v>6794071.91</v>
       </c>
       <c r="F5" t="n">
-        <v>54323582.47</v>
+        <v>46925257.53</v>
       </c>
       <c r="G5" t="n">
-        <v>66232576.85</v>
+        <v>58199596.55</v>
       </c>
       <c r="H5" t="n">
-        <v>31737857.21</v>
+        <v>9891960.16</v>
       </c>
       <c r="I5" t="n">
-        <v>54323582.47</v>
+        <v>46925257.53</v>
       </c>
       <c r="J5" t="n">
-        <v>58102150.03</v>
+        <v>51405524.64</v>
       </c>
       <c r="K5" t="n">
-        <v>66232576.85</v>
+        <v>52504542.61</v>
       </c>
       <c r="L5" t="n">
-        <v>58102150.03</v>
+        <v>51405524.64</v>
       </c>
       <c r="M5" t="n">
-        <v>58102150.03</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>51405524.64</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.01</v>
+      </c>
       <c r="O5" t="n">
-        <v>12802150.03</v>
+        <v>6105524.64</v>
       </c>
       <c r="P5" t="n">
         <v>40250000</v>
@@ -2014,128 +2051,292 @@
         <v>4750000</v>
       </c>
       <c r="S5" t="n">
-        <v>19025575.34</v>
+        <v>17617987.31</v>
       </c>
       <c r="T5" t="n">
-        <v>11180506.6</v>
+        <v>5792780.37</v>
       </c>
       <c r="U5" t="n">
-        <v>1743915.52</v>
+        <v>3912446.49</v>
       </c>
       <c r="V5" t="n">
-        <v>1306164.26</v>
+        <v>781315.91</v>
       </c>
       <c r="W5" t="n">
-        <v>8130426.82</v>
+        <v>1099017.97</v>
       </c>
       <c r="X5" t="n">
-        <v>8130426.82</v>
+        <v>1099017.97</v>
       </c>
       <c r="Y5" t="n">
-        <v>7845068.74</v>
+        <v>11825206.94</v>
       </c>
       <c r="Z5" t="n">
-        <v>2018241.11</v>
+        <v>1655000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1765000</v>
+        <v>5695053.94</v>
       </c>
       <c r="AB5" t="n">
-        <v>1765000</v>
+        <v>5695053.94</v>
       </c>
       <c r="AC5" t="n">
-        <v>374.88</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1289266.83</v>
+        <v>2338157.65</v>
       </c>
       <c r="AE5" t="n">
-        <v>4474006.5</v>
+        <v>3174163.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>129281.66</v>
+        <v>864652.48</v>
       </c>
       <c r="AG5" t="n">
-        <v>4474006.5</v>
+        <v>2309511.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>77127725.37</v>
+        <v>69023511.95</v>
       </c>
       <c r="AI5" t="n">
-        <v>37544799.42</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>211242.83</v>
-      </c>
+        <v>47306344.85</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>3778567.56</v>
+        <v>4480267.11</v>
       </c>
       <c r="AL5" t="n">
-        <v>430644.25</v>
+        <v>2677098.88</v>
       </c>
       <c r="AM5" t="n">
-        <v>3347923.31</v>
+        <v>1803168.23</v>
       </c>
       <c r="AN5" t="n">
-        <v>33554989.03</v>
+        <v>42826077.74</v>
       </c>
       <c r="AO5" t="n">
-        <v>-55342343.23</v>
+        <v>-66840651.38</v>
       </c>
       <c r="AP5" t="n">
-        <v>88897332.26000001</v>
+        <v>109666729.12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3226263.53</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>66639754.54</v>
-      </c>
+        <v>16312845.74</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>66639754.54</v>
+        <v>73516961.72</v>
       </c>
       <c r="AT5" t="n">
-        <v>19031314.19</v>
+        <v>19836921.66</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>39582925.95</v>
+        <v>21717167.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>730524.13</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+        <v>421500.44</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>190764</v>
+      </c>
       <c r="AY5" t="n">
-        <v>13947370.19</v>
+        <v>13655602.38</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3472145.91</v>
+        <v>3081698.04</v>
       </c>
       <c r="BA5" t="n">
-        <v>400447.36</v>
+        <v>4645652.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>10074776.92</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>211242.83</v>
-      </c>
+        <v>5928252.33</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>6977732.72</v>
+        <v>6545464.56</v>
       </c>
       <c r="BE5" t="n">
-        <v>17927298.91</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>10504957.5</v>
-      </c>
+        <v>903835.72</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>7422341.41</v>
+        <v>903835.72</v>
       </c>
       <c r="BH5" t="n">
-        <v>7422341.41</v>
+        <v>903835.72</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>2987326.71</v>
+      </c>
+      <c r="F6" t="n">
+        <v>46065538.09</v>
+      </c>
+      <c r="G6" t="n">
+        <v>54398559.58</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4385395.16</v>
+      </c>
+      <c r="I6" t="n">
+        <v>46065538.09</v>
+      </c>
+      <c r="J6" t="n">
+        <v>51411232.87</v>
+      </c>
+      <c r="K6" t="n">
+        <v>51720232.87</v>
+      </c>
+      <c r="L6" t="n">
+        <v>51411232.87</v>
+      </c>
+      <c r="M6" t="n">
+        <v>51411232.87</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>6111232.87</v>
+      </c>
+      <c r="P6" t="n">
+        <v>40250000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20696760.83</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5487717.81</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4267681.26</v>
+      </c>
+      <c r="V6" t="n">
+        <v>911036.55</v>
+      </c>
+      <c r="W6" t="n">
+        <v>309000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>309000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>15209043.02</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>639182.3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2678326.71</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2678326.71</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5579188.73</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>4362440.53</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>468901.8</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3893538.73</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>72107993.7</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>52513555.52</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>5345694.78</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4057444.91</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1288249.87</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>47167860.74</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-70360135.5</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>117527996.24</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>15084231.54</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>82092615.67</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>20351149.03</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>19594438.18</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>617317.35</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>262330.84</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>11519594.07</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3802214.44</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>3008934.52</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4708445.11</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="n">
+        <v>4079848.62</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>3115347.3</v>
+      </c>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="n">
+        <v>3115347.3</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3115347.3</v>
       </c>
     </row>
   </sheetData>
@@ -2149,7 +2350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2366,472 +2567,547 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2329000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-2621000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1318000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>-6988000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>904000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>25500000</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>380000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>524000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-1821000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>-518000</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>48000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>-1303000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-1303000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-2621000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1318000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-6972000</v>
-      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>25500000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>25500000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>-10513000</v>
+      </c>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>-1549000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-1549000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-5424000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>15000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-5439000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>9317000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-1433000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>9975000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>976000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>9573000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>312000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1013000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>4766000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>4766000</v>
-      </c>
+      <c r="AA2" t="n">
+        <v>-10513000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>-11000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-5305000</v>
-      </c>
+        <v>4000</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-4918000</v>
+        <v>-13298000</v>
       </c>
       <c r="C3" t="n">
-        <v>-2168000</v>
+        <v>-2176000</v>
       </c>
       <c r="D3" t="n">
-        <v>3874000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
       <c r="F3" t="n">
-        <v>-7330000</v>
+        <v>-10028000</v>
       </c>
       <c r="G3" t="n">
-        <v>380000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-1000</v>
-      </c>
+        <v>3127000</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>3127000</v>
+        <v>7422000</v>
       </c>
       <c r="J3" t="n">
-        <v>-2746000</v>
+        <v>-4295000</v>
       </c>
       <c r="K3" t="n">
-        <v>1103000</v>
+        <v>-1541000</v>
       </c>
       <c r="L3" t="n">
-        <v>3874000</v>
+        <v>857000</v>
       </c>
       <c r="M3" t="n">
-        <v>-413000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-190000</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-190000</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+        <v>-222000</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
       <c r="R3" t="n">
-        <v>1706000</v>
+        <v>-2176000</v>
       </c>
       <c r="S3" t="n">
-        <v>1706000</v>
+        <v>-2176000</v>
       </c>
       <c r="T3" t="n">
-        <v>-2168000</v>
+        <v>-2176000</v>
       </c>
       <c r="U3" t="n">
-        <v>3874000</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-6261000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1005000</v>
-      </c>
+        <v>516000</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>9000</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>10505000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>10505000</v>
+      </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>-654000</v>
+        <v>-438000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-654000</v>
+        <v>-438000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-6621000</v>
+        <v>-9552000</v>
       </c>
       <c r="AE3" t="n">
-        <v>55000</v>
+        <v>38000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-6676000</v>
+        <v>-9590000</v>
       </c>
       <c r="AG3" t="n">
-        <v>2412000</v>
+        <v>-3270000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-175000</v>
+        <v>-275000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-79000</v>
+        <v>-7726000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-933000</v>
+        <v>-1348000</v>
       </c>
       <c r="AK3" t="n">
-        <v>270000</v>
+        <v>-7345000</v>
       </c>
       <c r="AL3" t="n">
-        <v>168000</v>
+        <v>-1648000</v>
       </c>
       <c r="AM3" t="n">
-        <v>223000</v>
+        <v>344000</v>
       </c>
       <c r="AN3" t="n">
-        <v>4749000</v>
+        <v>4750000</v>
       </c>
       <c r="AO3" t="n">
-        <v>4749000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>12000</v>
-      </c>
+        <v>4750000</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>-2486000</v>
+        <v>1285000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-13298000</v>
+        <v>-4918000</v>
       </c>
       <c r="C4" t="n">
-        <v>-2176000</v>
+        <v>-2168000</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>3874000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-10028000</v>
+        <v>-7330000</v>
       </c>
       <c r="G4" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="I4" t="n">
         <v>3127000</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>7422000</v>
-      </c>
       <c r="J4" t="n">
-        <v>-4295000</v>
+        <v>-2746000</v>
       </c>
       <c r="K4" t="n">
-        <v>-1541000</v>
+        <v>1103000</v>
       </c>
       <c r="L4" t="n">
-        <v>857000</v>
+        <v>3874000</v>
       </c>
       <c r="M4" t="n">
-        <v>-222000</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
+        <v>-413000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-190000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-190000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>-2176000</v>
+        <v>1706000</v>
       </c>
       <c r="S4" t="n">
-        <v>-2176000</v>
+        <v>1706000</v>
       </c>
       <c r="T4" t="n">
-        <v>-2176000</v>
+        <v>-2168000</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3874000</v>
       </c>
       <c r="V4" t="n">
-        <v>516000</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>-6261000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1005000</v>
+      </c>
       <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>10505000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>10505000</v>
-      </c>
+        <v>9000</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>-438000</v>
+        <v>-654000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-438000</v>
+        <v>-654000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-9552000</v>
+        <v>-6621000</v>
       </c>
       <c r="AE4" t="n">
-        <v>38000</v>
+        <v>55000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-9590000</v>
+        <v>-6676000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3270000</v>
+        <v>2412000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-275000</v>
+        <v>-175000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-7726000</v>
+        <v>-79000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-1348000</v>
+        <v>-933000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-7345000</v>
+        <v>270000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1648000</v>
+        <v>168000</v>
       </c>
       <c r="AM4" t="n">
-        <v>344000</v>
+        <v>223000</v>
       </c>
       <c r="AN4" t="n">
-        <v>4750000</v>
+        <v>4749000</v>
       </c>
       <c r="AO4" t="n">
-        <v>4750000</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>4749000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>12000</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>1285000</v>
+        <v>-2486000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-5674000</v>
+        <v>2329000</v>
       </c>
       <c r="C5" t="n">
-        <v>-6006000</v>
+        <v>-2621000</v>
       </c>
       <c r="D5" t="n">
-        <v>2000000</v>
+        <v>1318000</v>
       </c>
       <c r="E5" t="n">
-        <v>25500000</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-4545000</v>
+        <v>-6988000</v>
       </c>
       <c r="G5" t="n">
-        <v>7422000</v>
+        <v>904000</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>2499000</v>
+        <v>380000</v>
       </c>
       <c r="J5" t="n">
-        <v>4923000</v>
+        <v>524000</v>
       </c>
       <c r="K5" t="n">
-        <v>21067000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>48000</v>
-      </c>
+        <v>-1821000</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>-475000</v>
+        <v>-518000</v>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
       <c r="P5" t="n">
-        <v>25500000</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>25500000</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-4006000</v>
+        <v>-1303000</v>
       </c>
       <c r="S5" t="n">
-        <v>-4006000</v>
+        <v>-1303000</v>
       </c>
       <c r="T5" t="n">
-        <v>-6006000</v>
+        <v>-2621000</v>
       </c>
       <c r="U5" t="n">
-        <v>2000000</v>
+        <v>1318000</v>
       </c>
       <c r="V5" t="n">
-        <v>-15015000</v>
+        <v>-6972000</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>26000</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-10513000</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="n">
-        <v>-10513000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>-233000</v>
+        <v>-1549000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-233000</v>
+        <v>-1549000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-4295000</v>
+        <v>-5424000</v>
       </c>
       <c r="AE5" t="n">
-        <v>17000</v>
+        <v>15000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-4312000</v>
+        <v>-5439000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1129000</v>
+        <v>9317000</v>
       </c>
       <c r="AH5" t="n">
-        <v>82000</v>
+        <v>-1433000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-6422000</v>
+        <v>9975000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2223000</v>
+        <v>976000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-8724000</v>
+        <v>9573000</v>
       </c>
       <c r="AL5" t="n">
-        <v>162000</v>
+        <v>312000</v>
       </c>
       <c r="AM5" t="n">
-        <v>687000</v>
+        <v>1013000</v>
       </c>
       <c r="AN5" t="n">
-        <v>4593000</v>
+        <v>4766000</v>
       </c>
       <c r="AO5" t="n">
-        <v>4593000</v>
+        <v>4766000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4000</v>
+        <v>-11000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-235000</v>
+        <v>-5305000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4638000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-3807000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-9846000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3115000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>904000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2212000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-4185000</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>-378000</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-3807000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-3807000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-3807000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-8087000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1433000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>286000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>-1787000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-1787000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-8019000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-8059000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>14484000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>64000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>9854000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2279000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>4334000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-105000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>66000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>4608000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>4608000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>6000</v>
       </c>
     </row>
   </sheetData>
@@ -3326,197 +3602,197 @@
       </c>
       <c r="CR1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>shortName</t>
         </is>
       </c>
       <c r="EE1" t="inlineStr">
@@ -3536,10 +3812,8 @@
           <t>Weimar</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>99425</t>
-        </is>
+      <c r="C2" t="n">
+        <v>99425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3590,37 +3864,37 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>16.4</v>
+        <v>17.3</v>
       </c>
       <c r="S2" t="n">
-        <v>16.45</v>
+        <v>16.2</v>
       </c>
       <c r="T2" t="n">
-        <v>16.45</v>
+        <v>16.2</v>
       </c>
       <c r="U2" t="n">
-        <v>16.6</v>
+        <v>16.2</v>
       </c>
       <c r="V2" t="n">
-        <v>16.4</v>
+        <v>17.3</v>
       </c>
       <c r="W2" t="n">
-        <v>16.45</v>
+        <v>16.2</v>
       </c>
       <c r="X2" t="n">
-        <v>16.45</v>
+        <v>16.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.6</v>
+        <v>16.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.888</v>
+        <v>1.891</v>
       </c>
       <c r="AA2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC2" t="n">
         <v>45</v>
@@ -3638,10 +3912,10 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>87120656</v>
+        <v>85536656</v>
       </c>
       <c r="AI2" t="n">
-        <v>77900000</v>
+        <v>78850000</v>
       </c>
       <c r="AJ2" t="n">
         <v>9.359999999999999</v>
@@ -3656,7 +3930,7 @@
         <v>9.359999999999999</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.9078743</v>
+        <v>1.873186</v>
       </c>
       <c r="AO2" t="n">
         <v>12.124367</v>
@@ -3668,7 +3942,7 @@
         <v>0.12</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.007317073</v>
+        <v>0.0069364165</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -3679,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>78246976</v>
+        <v>84184480</v>
       </c>
       <c r="AV2" t="n">
         <v>0.00013</v>
@@ -3703,7 +3977,7 @@
         <v>10.823</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.5245311</v>
+        <v>1.4968125</v>
       </c>
       <c r="BD2" t="n">
         <v>1767139200</v>
@@ -3721,16 +3995,16 @@
         <v>-0.52</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.714</v>
+        <v>1.844</v>
       </c>
       <c r="BJ2" t="n">
-        <v>16.682</v>
+        <v>17.948</v>
       </c>
       <c r="BK2" t="n">
         <v>-0.44445843</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.27294624</v>
+        <v>0.2568333</v>
       </c>
       <c r="BM2" t="n">
         <v>0.12</v>
@@ -3744,7 +4018,7 @@
         </is>
       </c>
       <c r="BP2" t="n">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
@@ -3843,146 +4117,146 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CR2" t="n">
-        <v>0.60975844</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="CT2" t="b">
-        <v>0</v>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>IBU-tec advanced materials AG</t>
+        </is>
+      </c>
+      <c r="CS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>IBU TEC ADVANCED MATERIALS AG I</t>
+        </is>
       </c>
       <c r="CU2" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>4.075634</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>0.33615232</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>-1.7364388</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>-0.09681067</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="n">
         <v>1636963200000</v>
       </c>
-      <c r="CV2" t="n">
-        <v>0.10000038</v>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>16.45 - 16.6</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
+      <c r="DE2" t="n">
+        <v>-1.0999985</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>16.2 - 16.2</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
         <is>
           <t>LSE</t>
         </is>
       </c>
-      <c r="CY2" t="n">
+      <c r="DH2" t="n">
         <v>45</v>
       </c>
-      <c r="CZ2" t="n">
-        <v>7.1400003</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>0.7628206</v>
-      </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DI2" t="n">
+        <v>6.840001</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.7307694</v>
+      </c>
+      <c r="DK2" t="inlineStr">
         <is>
           <t>9.36 - 27.4</t>
         </is>
       </c>
-      <c r="DC2" t="n">
-        <v>-10.9</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>-0.39781022</v>
-      </c>
-      <c r="DE2" t="n">
+      <c r="DL2" t="n">
+        <v>-11.199999</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.4087591</v>
+      </c>
+      <c r="DN2" t="n">
         <v>-44.445843</v>
       </c>
-      <c r="DF2" t="n">
+      <c r="DO2" t="n">
         <v>1756103776</v>
       </c>
-      <c r="DG2" t="n">
+      <c r="DP2" t="n">
         <v>1756449376</v>
       </c>
-      <c r="DH2" t="n">
+      <c r="DQ2" t="n">
         <v>1711099800</v>
       </c>
-      <c r="DI2" t="n">
+      <c r="DR2" t="n">
         <v>1711099800</v>
       </c>
-      <c r="DJ2" t="b">
+      <c r="DS2" t="b">
         <v>1</v>
       </c>
-      <c r="DK2" t="n">
-        <v>-0.08008498999999999</v>
-      </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DT2" t="n">
+        <v>-6.358373</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="DV2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DM2" t="n">
-        <v>1780316951</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DW2" t="n">
+        <v>1781881397</v>
+      </c>
+      <c r="DX2" t="inlineStr">
         <is>
           <t>LSE</t>
         </is>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>finmb_106933772</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>Europe/London</t>
         </is>
       </c>
-      <c r="DR2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>BST</t>
         </is>
       </c>
-      <c r="DS2" t="n">
+      <c r="EB2" t="n">
         <v>3600000</v>
       </c>
-      <c r="DT2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>gb_market</t>
         </is>
       </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>4.3756332</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>0.3608958</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-1.4364395</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>IBU-tec advanced materials AG</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>IBU TEC ADVANCED MATERIALS AG I</t>
-        </is>
+      <c r="ED2" t="b">
+        <v>0</v>
       </c>
       <c r="EE2" t="inlineStr"/>
     </row>
